--- a/Deliverables/BOM/BOM-V2.1-wo-Battery/eSpark-BOM-v2.1_Wo_Battery Boards.xlsx
+++ b/Deliverables/BOM/BOM-V2.1-wo-Battery/eSpark-BOM-v2.1_Wo_Battery Boards.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\BOM-V2.1-wo-Battery\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54539A64-E3ED-4A68-9854-348A4926C195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7084DFAE-A0A3-4EEA-8DD6-C5ECEC686904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="20 Boards" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="223">
   <si>
     <t>Component list</t>
   </si>
@@ -8263,7 +8263,7 @@
       <c r="S35" s="103"/>
       <c r="X35"/>
     </row>
-    <row r="36" spans="1:24" s="101" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" s="101" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="98"/>
       <c r="B36" s="55">
         <f t="shared" si="1"/>
@@ -8291,7 +8291,7 @@
         <v>175</v>
       </c>
       <c r="J36" s="72" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="K36" s="50" t="s">
         <v>175</v>
@@ -8307,22 +8307,20 @@
         <v>10050</v>
       </c>
       <c r="O36" s="133" t="s">
-        <v>152</v>
+        <v>211</v>
       </c>
       <c r="P36" s="90">
-        <v>2.6855000000000002</v>
+        <v>4.78</v>
       </c>
       <c r="Q36" s="135">
         <f t="shared" si="3"/>
-        <v>26989.275000000001</v>
-      </c>
-      <c r="R36" s="138" t="s">
-        <v>216</v>
-      </c>
+        <v>48039</v>
+      </c>
+      <c r="R36" s="138"/>
       <c r="S36" s="100"/>
       <c r="X36"/>
     </row>
-    <row r="37" spans="1:24" s="101" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" s="101" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="98"/>
       <c r="B37" s="55">
         <f>ROW(B37) - ROW($B$9)</f>
@@ -8350,7 +8348,7 @@
         <v>175</v>
       </c>
       <c r="J37" s="77" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K37" s="40" t="s">
         <v>175</v>
@@ -8366,18 +8364,16 @@
         <v>5020</v>
       </c>
       <c r="O37" s="80" t="s">
-        <v>152</v>
+        <v>211</v>
       </c>
       <c r="P37" s="89">
-        <v>3.8199999999999998E-2</v>
+        <v>0.03</v>
       </c>
       <c r="Q37" s="102">
         <f t="shared" si="3"/>
-        <v>191.76399999999998</v>
-      </c>
-      <c r="R37" s="139" t="s">
-        <v>216</v>
-      </c>
+        <v>150.6</v>
+      </c>
+      <c r="R37" s="139"/>
       <c r="S37" s="103"/>
       <c r="X37"/>
     </row>
@@ -8520,7 +8516,7 @@
       <c r="P40" s="149"/>
       <c r="Q40" s="124">
         <f>SUM(Q10:Q39)</f>
-        <v>132385.02599999998</v>
+        <v>153393.587</v>
       </c>
       <c r="R40" s="144"/>
       <c r="S40" s="145"/>
@@ -8546,7 +8542,7 @@
       <c r="P41" s="149"/>
       <c r="Q41" s="125">
         <f>Q40/5000</f>
-        <v>26.477005199999997</v>
+        <v>30.6787174</v>
       </c>
       <c r="R41" s="146"/>
       <c r="S41" s="147"/>
@@ -8642,23 +8638,21 @@
     <hyperlink ref="O38" r:id="rId10" xr:uid="{3EEFCC48-686E-47C8-B7B8-E9E1C2DAFDA3}"/>
     <hyperlink ref="O39" r:id="rId11" xr:uid="{01DE47D8-FCD2-4A50-BDE1-30AAC5145A11}"/>
     <hyperlink ref="O34" r:id="rId12" xr:uid="{2AD914F5-A895-4E0B-9F83-5AED7AEAD741}"/>
-    <hyperlink ref="O37" r:id="rId13" xr:uid="{3ED337E1-DBE6-4820-AFE1-8EAD432DAC00}"/>
-    <hyperlink ref="O27" r:id="rId14" xr:uid="{B22C7605-5FFC-4FB9-860B-A31FAB521735}"/>
-    <hyperlink ref="O28" r:id="rId15" xr:uid="{0748075E-9E35-4ACF-8505-EA044D27BFDB}"/>
-    <hyperlink ref="O29" r:id="rId16" xr:uid="{38BD8283-B7F5-440F-8E55-273DC274C858}"/>
-    <hyperlink ref="O13" r:id="rId17" xr:uid="{ACB7EA74-DC46-4E8E-8B6B-C136A8E53E22}"/>
-    <hyperlink ref="O18" r:id="rId18" xr:uid="{45F79932-22EE-44A9-94B1-C34664FDC1D4}"/>
-    <hyperlink ref="O20" r:id="rId19" xr:uid="{78F083A5-11A9-4468-801A-729FDA85826B}"/>
-    <hyperlink ref="O23" r:id="rId20" xr:uid="{9D6D906C-6FF5-4464-B8EC-9797740B30E5}"/>
-    <hyperlink ref="O24" r:id="rId21" xr:uid="{5ED73709-63B8-410D-81BB-E3384DFF6150}"/>
-    <hyperlink ref="O26" r:id="rId22" xr:uid="{260528D6-F7D9-4C5B-9808-0D61E9031FAD}"/>
-    <hyperlink ref="O30" r:id="rId23" xr:uid="{45EB2636-CD73-4B4B-AFC5-733A0A0E6D3D}"/>
-    <hyperlink ref="O33" r:id="rId24" display="LCSC" xr:uid="{8ACB1CF9-90A7-4871-BE83-A0BE5DD099AF}"/>
-    <hyperlink ref="O36" r:id="rId25" xr:uid="{B33148BA-8C8B-4B3F-8EE4-C64AB425EC1D}"/>
-    <hyperlink ref="O17" r:id="rId26" xr:uid="{45382040-6624-4503-AD07-DC02A240843F}"/>
+    <hyperlink ref="O27" r:id="rId13" xr:uid="{B22C7605-5FFC-4FB9-860B-A31FAB521735}"/>
+    <hyperlink ref="O28" r:id="rId14" xr:uid="{0748075E-9E35-4ACF-8505-EA044D27BFDB}"/>
+    <hyperlink ref="O29" r:id="rId15" xr:uid="{38BD8283-B7F5-440F-8E55-273DC274C858}"/>
+    <hyperlink ref="O13" r:id="rId16" xr:uid="{ACB7EA74-DC46-4E8E-8B6B-C136A8E53E22}"/>
+    <hyperlink ref="O18" r:id="rId17" xr:uid="{45F79932-22EE-44A9-94B1-C34664FDC1D4}"/>
+    <hyperlink ref="O20" r:id="rId18" xr:uid="{78F083A5-11A9-4468-801A-729FDA85826B}"/>
+    <hyperlink ref="O23" r:id="rId19" xr:uid="{9D6D906C-6FF5-4464-B8EC-9797740B30E5}"/>
+    <hyperlink ref="O24" r:id="rId20" xr:uid="{5ED73709-63B8-410D-81BB-E3384DFF6150}"/>
+    <hyperlink ref="O26" r:id="rId21" xr:uid="{260528D6-F7D9-4C5B-9808-0D61E9031FAD}"/>
+    <hyperlink ref="O30" r:id="rId22" xr:uid="{45EB2636-CD73-4B4B-AFC5-733A0A0E6D3D}"/>
+    <hyperlink ref="O33" r:id="rId23" display="LCSC" xr:uid="{8ACB1CF9-90A7-4871-BE83-A0BE5DD099AF}"/>
+    <hyperlink ref="O17" r:id="rId24" xr:uid="{45382040-6624-4503-AD07-DC02A240843F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId27"/>
+  <drawing r:id="rId25"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
